--- a/Lab_4/src/results.xlsx
+++ b/Lab_4/src/results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
         <v>5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -573,13 +573,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -591,28 +591,28 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,22 +646,22 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -674,28 +674,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
@@ -704,19 +704,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -726,49 +726,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>17</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
         <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -790,37 +790,37 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -845,34 +845,34 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -891,25 +891,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>54</v>
+      </c>
+      <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
-        <v>18</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>39</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
         <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
@@ -1123,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1142,22 +1142,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
         <v>8</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1175,16 +1175,16 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1227,13 +1227,13 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,49 +1246,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14748,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17808,7 +17808,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22347,7 +22347,7 @@
       </c>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22738,7 +22738,7 @@
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22925,7 +22925,7 @@
       </c>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23095,7 +23095,7 @@
       </c>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23214,7 @@
       </c>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23656,7 +23656,7 @@
       </c>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23673,7 +23673,7 @@
       </c>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25543,7 +25543,7 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25560,7 +25560,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26155,7 +26155,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26376,7 +26376,7 @@
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26648,7 +26648,7 @@
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26716,7 +26716,7 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
